--- a/circuit.xlsx
+++ b/circuit.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,40 +469,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Secteur</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Longueur_m</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Angle_deg</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Debut_X</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Debut_Y</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Fin_X</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fin_Y</t>
         </is>
@@ -512,21 +517,21 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>ligne_des_stands</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>231.31</v>
-      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>379.27</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -535,9 +540,12 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>231.31</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>379.27</v>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -545,528 +553,1224 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>virage</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>virage_rapide</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>84.92</v>
-      </c>
       <c r="E3" t="n">
-        <v>33.96</v>
+        <v>88.42</v>
       </c>
       <c r="F3" t="n">
-        <v>231.31</v>
+        <v>-34.86</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>379.27</v>
       </c>
       <c r="H3" t="n">
-        <v>311.35</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>24.44</v>
+        <v>462.33</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-26.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>259.04</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>144.25</v>
       </c>
       <c r="F4" t="n">
-        <v>311.35</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>24.44</v>
+        <v>462.33</v>
       </c>
       <c r="H4" t="n">
-        <v>526.2</v>
+        <v>-26.08</v>
       </c>
       <c r="I4" t="n">
-        <v>169.14</v>
+        <v>580.6900000000001</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-108.54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>virage</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>virage_rapide</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>98.18000000000001</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>-44.29</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>526.2</v>
+        <v>-54.37</v>
       </c>
       <c r="G5" t="n">
-        <v>169.14</v>
+        <v>580.6900000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>619.92</v>
+        <v>-108.54</v>
       </c>
       <c r="I5" t="n">
-        <v>188.74</v>
+        <v>598.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-141.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="B6" t="n">
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>171.18</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>183.32</v>
       </c>
       <c r="F6" t="n">
-        <v>619.92</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>188.74</v>
+        <v>598.29</v>
       </c>
       <c r="H6" t="n">
-        <v>788.3200000000001</v>
+        <v>-141.71</v>
       </c>
       <c r="I6" t="n">
-        <v>158.03</v>
+        <v>600.73</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-325.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>virage</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>virage_lent</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>97.26000000000001</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>84.76000000000001</v>
+        <v>72.52</v>
       </c>
       <c r="F7" t="n">
-        <v>788.3200000000001</v>
+        <v>165.74</v>
       </c>
       <c r="G7" t="n">
-        <v>158.03</v>
+        <v>600.73</v>
       </c>
       <c r="H7" t="n">
-        <v>863.45</v>
+        <v>-325.02</v>
       </c>
       <c r="I7" t="n">
-        <v>205.06</v>
+        <v>650.1799999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-330.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>141.48</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>138.46</v>
       </c>
       <c r="F8" t="n">
-        <v>863.45</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>205.06</v>
+        <v>650.1799999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>901.4299999999999</v>
+        <v>-330.54</v>
       </c>
       <c r="I8" t="n">
-        <v>341.35</v>
+        <v>682.51</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-195.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>virage</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>virage_lent</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>84.66</v>
-      </c>
       <c r="E9" t="n">
-        <v>79.37</v>
+        <v>84.8</v>
       </c>
       <c r="F9" t="n">
-        <v>901.4299999999999</v>
+        <v>-63</v>
       </c>
       <c r="G9" t="n">
-        <v>341.35</v>
+        <v>682.51</v>
       </c>
       <c r="H9" t="n">
-        <v>869.55</v>
+        <v>-195.9</v>
       </c>
       <c r="I9" t="n">
-        <v>412.6</v>
+        <v>739.49</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-138.91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="B10" t="n">
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>94.98999999999999</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>168.56</v>
       </c>
       <c r="F10" t="n">
-        <v>869.55</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>412.6</v>
+        <v>739.49</v>
       </c>
       <c r="H10" t="n">
-        <v>784.3200000000001</v>
+        <v>-138.91</v>
       </c>
       <c r="I10" t="n">
-        <v>454.54</v>
+        <v>903.39</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-99.56999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>virage</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>virage_rapide</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>82.01000000000001</v>
-      </c>
       <c r="E11" t="n">
-        <v>-36.93</v>
+        <v>82.55</v>
       </c>
       <c r="F11" t="n">
-        <v>784.3200000000001</v>
+        <v>-40.01</v>
       </c>
       <c r="G11" t="n">
-        <v>454.54</v>
+        <v>903.39</v>
       </c>
       <c r="H11" t="n">
-        <v>727</v>
+        <v>-99.56999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>511.2</v>
+        <v>983.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-108.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>105.37</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>132.73</v>
       </c>
       <c r="F12" t="n">
-        <v>727</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>511.2</v>
+        <v>983.75</v>
       </c>
       <c r="H12" t="n">
-        <v>679.38</v>
+        <v>-108.73</v>
       </c>
       <c r="I12" t="n">
-        <v>605.2</v>
+        <v>1102.53</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-167.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>virage</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>virage_rapide</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>62.19</v>
-      </c>
       <c r="E13" t="n">
-        <v>39.58</v>
+        <v>99.47</v>
       </c>
       <c r="F13" t="n">
-        <v>679.38</v>
+        <v>40.86</v>
       </c>
       <c r="G13" t="n">
-        <v>605.2</v>
+        <v>1102.53</v>
       </c>
       <c r="H13" t="n">
-        <v>635.05</v>
+        <v>-167.98</v>
       </c>
       <c r="I13" t="n">
-        <v>647.04</v>
+        <v>1199.36</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-178.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>127.79</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>122.94</v>
       </c>
       <c r="F14" t="n">
-        <v>635.05</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>647.04</v>
+        <v>1199.36</v>
       </c>
       <c r="H14" t="n">
-        <v>517.9</v>
+        <v>-178.3</v>
       </c>
       <c r="I14" t="n">
-        <v>698.1</v>
+        <v>1318.46</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-147.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>virage</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>epingle</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>56.73</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>131.49</v>
+        <v>44.91</v>
       </c>
       <c r="F15" t="n">
-        <v>517.9</v>
+        <v>-58.89</v>
       </c>
       <c r="G15" t="n">
-        <v>698.1</v>
+        <v>1318.46</v>
       </c>
       <c r="H15" t="n">
-        <v>484.51</v>
+        <v>-147.84</v>
       </c>
       <c r="I15" t="n">
-        <v>667.83</v>
+        <v>1359.94</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-159.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>131.16</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>108.23</v>
       </c>
       <c r="F16" t="n">
-        <v>484.51</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>667.83</v>
+        <v>1359.94</v>
       </c>
       <c r="H16" t="n">
-        <v>524.92</v>
+        <v>-159.03</v>
       </c>
       <c r="I16" t="n">
-        <v>543.05</v>
+        <v>1437.08</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-234.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>virage</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>virage_rapide</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>79.15000000000001</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
       </c>
       <c r="E17" t="n">
-        <v>-43.72</v>
+        <v>102.38</v>
       </c>
       <c r="F17" t="n">
-        <v>524.92</v>
+        <v>-77</v>
       </c>
       <c r="G17" t="n">
-        <v>543.05</v>
+        <v>1437.08</v>
       </c>
       <c r="H17" t="n">
-        <v>519.64</v>
+        <v>-234.95</v>
       </c>
       <c r="I17" t="n">
-        <v>465.98</v>
+        <v>1448.56</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-329.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>143.26</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1448.56</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-329.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1373.61</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-451.19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-62.57</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1373.61</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-451.19</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1315.31</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-481.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>99.14</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1315.31</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-481.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1216.43</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-473.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-52.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1216.43</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-473.98</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1183.51</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-454.83</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>224.34</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1183.51</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-454.83</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1058.78</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-268.36</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>89.37</v>
+      </c>
+      <c r="F23" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1058.78</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-268.36</v>
+      </c>
+      <c r="I23" t="n">
+        <v>980.48</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-238.45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>152.35</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>980.48</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-238.45</v>
+      </c>
+      <c r="I24" t="n">
+        <v>832.9299999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-276.36</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>virage_rapide</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="G25" t="n">
+        <v>832.9299999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-276.36</v>
+      </c>
+      <c r="I25" t="n">
+        <v>770.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-313.53</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>161.86</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>770.3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-313.53</v>
+      </c>
+      <c r="I26" t="n">
+        <v>659.85</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-431.86</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>virage_rapide</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-31.13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>659.85</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-431.86</v>
+      </c>
+      <c r="I27" t="n">
+        <v>599.03</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-468.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>257.57</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>599.03</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-468.99</v>
+      </c>
+      <c r="I28" t="n">
+        <v>351.24</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-539.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-38.27</v>
+      </c>
+      <c r="G29" t="n">
+        <v>351.24</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-539.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>325.41</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-537.8200000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>325.41</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-537.8200000000001</v>
+      </c>
+      <c r="I30" t="n">
+        <v>253.06</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-507.96</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="F31" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="G31" t="n">
+        <v>253.06</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-507.96</v>
+      </c>
+      <c r="I31" t="n">
+        <v>227.89</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-505.16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>233.48</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>227.89</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-505.16</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-544.63</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-29.52</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-544.63</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-31.01</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-542.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-31.01</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-542.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-101.96</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-516.58</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="F35" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-101.96</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-516.58</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-134.06</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-517.21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>retour_stands</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>697.97</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>519.64</v>
-      </c>
-      <c r="G18" t="n">
-        <v>465.98</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="E36" t="n">
+        <v>534.3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-134.06</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-517.21</v>
+      </c>
+      <c r="I36" t="n">
         <v>-0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/circuit.xlsx
+++ b/circuit.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,45 +469,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Secteur</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Categorie</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Categorie</t>
+          <t>Longueur_m</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Longueur_m</t>
+          <t>Angle_deg</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Angle_deg</t>
+          <t>Debut_X</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Debut_X</t>
+          <t>Debut_Y</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Debut_Y</t>
+          <t>Fin_X</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Fin_X</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Fin_Y</t>
         </is>
@@ -517,21 +512,21 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ligne_droite</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>ligne_des_stands</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>285.06</v>
+      </c>
       <c r="E2" t="n">
-        <v>379.27</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -540,12 +535,9 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>285.06</v>
       </c>
       <c r="I2" t="n">
-        <v>379.27</v>
-      </c>
-      <c r="J2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -553,1223 +545,1649 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>virage_rapide</t>
-        </is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>35.06</v>
       </c>
       <c r="E3" t="n">
-        <v>88.42</v>
+        <v>40.26</v>
       </c>
       <c r="F3" t="n">
-        <v>-34.86</v>
+        <v>285.06</v>
       </c>
       <c r="G3" t="n">
-        <v>379.27</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>317.3</v>
       </c>
       <c r="I3" t="n">
-        <v>462.33</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-26.08</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ligne_droite</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>53.46</v>
       </c>
       <c r="E4" t="n">
-        <v>144.25</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>317.3</v>
       </c>
       <c r="G4" t="n">
-        <v>462.33</v>
+        <v>11.82</v>
       </c>
       <c r="H4" t="n">
-        <v>-26.08</v>
+        <v>358.09</v>
       </c>
       <c r="I4" t="n">
-        <v>580.6900000000001</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-108.54</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>virage_lent</t>
-        </is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>16.57</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>-31.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-54.37</v>
+        <v>358.09</v>
       </c>
       <c r="G5" t="n">
-        <v>580.6900000000001</v>
+        <v>46.37</v>
       </c>
       <c r="H5" t="n">
-        <v>-108.54</v>
+        <v>372.97</v>
       </c>
       <c r="I5" t="n">
-        <v>598.29</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-141.71</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="D6" t="n">
+        <v>159.79</v>
       </c>
       <c r="E6" t="n">
-        <v>183.32</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>372.97</v>
       </c>
       <c r="G6" t="n">
-        <v>598.29</v>
+        <v>53.16</v>
       </c>
       <c r="H6" t="n">
-        <v>-141.71</v>
+        <v>530.9</v>
       </c>
       <c r="I6" t="n">
-        <v>600.73</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-325.02</v>
+        <v>77.51000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>epingle</t>
-        </is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>92.91</v>
       </c>
       <c r="E7" t="n">
-        <v>72.52</v>
+        <v>93.81</v>
       </c>
       <c r="F7" t="n">
-        <v>165.74</v>
+        <v>530.9</v>
       </c>
       <c r="G7" t="n">
-        <v>600.73</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-325.02</v>
+        <v>577.63</v>
       </c>
       <c r="I7" t="n">
-        <v>650.1799999999999</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-330.54</v>
+        <v>145.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="D8" t="n">
+        <v>204.78</v>
       </c>
       <c r="E8" t="n">
-        <v>138.46</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>577.63</v>
       </c>
       <c r="G8" t="n">
-        <v>650.1799999999999</v>
+        <v>145.95</v>
       </c>
       <c r="H8" t="n">
-        <v>-330.54</v>
+        <v>533.04</v>
       </c>
       <c r="I8" t="n">
-        <v>682.51</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-195.9</v>
+        <v>345.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>virage_lent</t>
-        </is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>31.18</v>
       </c>
       <c r="E9" t="n">
-        <v>84.8</v>
+        <v>32.53</v>
       </c>
       <c r="F9" t="n">
-        <v>-63</v>
+        <v>533.04</v>
       </c>
       <c r="G9" t="n">
-        <v>682.51</v>
+        <v>345.82</v>
       </c>
       <c r="H9" t="n">
-        <v>-195.9</v>
+        <v>518.1900000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>739.49</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-138.91</v>
+        <v>372.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ligne_droite</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>53.77</v>
       </c>
       <c r="E10" t="n">
-        <v>168.56</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>518.1900000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>739.49</v>
+        <v>372.77</v>
       </c>
       <c r="H10" t="n">
-        <v>-138.91</v>
+        <v>480.1</v>
       </c>
       <c r="I10" t="n">
-        <v>903.39</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-99.56999999999999</v>
+        <v>410.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>virage_rapide</t>
-        </is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>29.88</v>
       </c>
       <c r="E11" t="n">
-        <v>82.55</v>
+        <v>-33.95</v>
       </c>
       <c r="F11" t="n">
-        <v>-40.01</v>
+        <v>480.1</v>
       </c>
       <c r="G11" t="n">
-        <v>903.39</v>
+        <v>410.72</v>
       </c>
       <c r="H11" t="n">
-        <v>-99.56999999999999</v>
+        <v>466.22</v>
       </c>
       <c r="I11" t="n">
-        <v>983.75</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-108.73</v>
+        <v>436.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="D12" t="n">
+        <v>132.75</v>
       </c>
       <c r="E12" t="n">
-        <v>132.73</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>466.22</v>
       </c>
       <c r="G12" t="n">
-        <v>983.75</v>
+        <v>436.69</v>
       </c>
       <c r="H12" t="n">
-        <v>-108.73</v>
+        <v>440.53</v>
       </c>
       <c r="I12" t="n">
-        <v>1102.53</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-167.98</v>
+        <v>566.9299999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
-        <v>2</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
           <t>virage_rapide</t>
         </is>
       </c>
+      <c r="D13" t="n">
+        <v>85.2</v>
+      </c>
       <c r="E13" t="n">
-        <v>99.47</v>
+        <v>-39.58</v>
       </c>
       <c r="F13" t="n">
-        <v>40.86</v>
+        <v>440.53</v>
       </c>
       <c r="G13" t="n">
-        <v>1102.53</v>
+        <v>566.9299999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-167.98</v>
+        <v>453.06</v>
       </c>
       <c r="I13" t="n">
-        <v>1199.36</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-178.3</v>
+        <v>649.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
-        <v>2</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="D14" t="n">
+        <v>153.46</v>
       </c>
       <c r="E14" t="n">
-        <v>122.94</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>453.06</v>
       </c>
       <c r="G14" t="n">
-        <v>1199.36</v>
+        <v>649.5</v>
       </c>
       <c r="H14" t="n">
-        <v>-178.3</v>
+        <v>526.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1318.46</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-147.84</v>
+        <v>784.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
-        <v>2</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>virage_lent</t>
-        </is>
+          <t>virage_rapide</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>80.17</v>
       </c>
       <c r="E15" t="n">
-        <v>44.91</v>
+        <v>32.04</v>
       </c>
       <c r="F15" t="n">
-        <v>-58.89</v>
+        <v>526.1</v>
       </c>
       <c r="G15" t="n">
-        <v>1318.46</v>
+        <v>784.47</v>
       </c>
       <c r="H15" t="n">
-        <v>-147.84</v>
+        <v>543.08</v>
       </c>
       <c r="I15" t="n">
-        <v>1359.94</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-159.03</v>
+        <v>861.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
-        <v>2</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="D16" t="n">
+        <v>149.27</v>
       </c>
       <c r="E16" t="n">
-        <v>108.23</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>543.08</v>
       </c>
       <c r="G16" t="n">
-        <v>1359.94</v>
+        <v>861.75</v>
       </c>
       <c r="H16" t="n">
-        <v>-159.03</v>
+        <v>533.65</v>
       </c>
       <c r="I16" t="n">
-        <v>1437.08</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-234.95</v>
+        <v>1010.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
-        <v>2</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
           <t>virage_lent</t>
         </is>
       </c>
+      <c r="D17" t="n">
+        <v>100.63</v>
+      </c>
       <c r="E17" t="n">
-        <v>102.38</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-77</v>
+        <v>533.65</v>
       </c>
       <c r="G17" t="n">
-        <v>1437.08</v>
+        <v>1010.72</v>
       </c>
       <c r="H17" t="n">
-        <v>-234.95</v>
+        <v>464.88</v>
       </c>
       <c r="I17" t="n">
-        <v>1448.56</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-329.1</v>
+        <v>1068.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
-        <v>2</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="D18" t="n">
+        <v>123.09</v>
       </c>
       <c r="E18" t="n">
-        <v>143.26</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>464.88</v>
       </c>
       <c r="G18" t="n">
-        <v>1448.56</v>
+        <v>1068.94</v>
       </c>
       <c r="H18" t="n">
-        <v>-329.1</v>
+        <v>342.44</v>
       </c>
       <c r="I18" t="n">
-        <v>1373.61</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-451.19</v>
+        <v>1056.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
-        <v>2</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>virage_lent</t>
-        </is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>22.13</v>
       </c>
       <c r="E19" t="n">
-        <v>68.89</v>
+        <v>42.12</v>
       </c>
       <c r="F19" t="n">
-        <v>-62.57</v>
+        <v>342.44</v>
       </c>
       <c r="G19" t="n">
-        <v>1373.61</v>
+        <v>1056.33</v>
       </c>
       <c r="H19" t="n">
-        <v>-451.19</v>
+        <v>323.15</v>
       </c>
       <c r="I19" t="n">
-        <v>1315.31</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-481.1</v>
+        <v>1046.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
-        <v>2</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ligne_droite</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>63.31</v>
       </c>
       <c r="E20" t="n">
-        <v>99.14</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>323.15</v>
       </c>
       <c r="G20" t="n">
-        <v>1315.31</v>
+        <v>1046.52</v>
       </c>
       <c r="H20" t="n">
-        <v>-481.1</v>
+        <v>280.78</v>
       </c>
       <c r="I20" t="n">
-        <v>1216.43</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-473.98</v>
+        <v>999.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
-        <v>2</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>virage_lent</t>
-        </is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>39.43</v>
+        <v>-38.39</v>
       </c>
       <c r="F21" t="n">
-        <v>-52.1</v>
+        <v>280.78</v>
       </c>
       <c r="G21" t="n">
-        <v>1216.43</v>
+        <v>999.47</v>
       </c>
       <c r="H21" t="n">
-        <v>-473.98</v>
+        <v>249.82</v>
       </c>
       <c r="I21" t="n">
-        <v>1183.51</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-454.83</v>
+        <v>982.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
-        <v>2</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="D22" t="n">
+        <v>206.34</v>
       </c>
       <c r="E22" t="n">
-        <v>224.34</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>249.82</v>
       </c>
       <c r="G22" t="n">
-        <v>1183.51</v>
+        <v>982.45</v>
       </c>
       <c r="H22" t="n">
-        <v>-454.83</v>
+        <v>46.37</v>
       </c>
       <c r="I22" t="n">
-        <v>1058.78</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-268.36</v>
+        <v>948</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
-        <v>2</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>virage_lent</t>
-        </is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>35.28</v>
       </c>
       <c r="E23" t="n">
-        <v>89.37</v>
+        <v>-40.17</v>
       </c>
       <c r="F23" t="n">
-        <v>70.63</v>
+        <v>46.37</v>
       </c>
       <c r="G23" t="n">
-        <v>1058.78</v>
+        <v>948</v>
       </c>
       <c r="H23" t="n">
-        <v>-268.36</v>
+        <v>12.39</v>
       </c>
       <c r="I23" t="n">
-        <v>980.48</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-238.45</v>
+        <v>954.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
-        <v>2</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ligne_droite</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>53.74</v>
       </c>
       <c r="E24" t="n">
-        <v>152.35</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>12.39</v>
       </c>
       <c r="G24" t="n">
-        <v>980.48</v>
+        <v>954.29</v>
       </c>
       <c r="H24" t="n">
-        <v>-238.45</v>
+        <v>-33.88</v>
       </c>
       <c r="I24" t="n">
-        <v>832.9299999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-276.36</v>
+        <v>981.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
-        <v>2</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>virage_rapide</t>
-        </is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>29.11</v>
       </c>
       <c r="E25" t="n">
-        <v>73.81999999999999</v>
+        <v>39.41</v>
       </c>
       <c r="F25" t="n">
-        <v>32.56</v>
+        <v>-33.88</v>
       </c>
       <c r="G25" t="n">
-        <v>832.9299999999999</v>
+        <v>981.61</v>
       </c>
       <c r="H25" t="n">
-        <v>-276.36</v>
+        <v>-61.91</v>
       </c>
       <c r="I25" t="n">
-        <v>770.3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-313.53</v>
+        <v>986.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
-        <v>3</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="D26" t="n">
+        <v>150.22</v>
       </c>
       <c r="E26" t="n">
-        <v>161.86</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-61.91</v>
       </c>
       <c r="G26" t="n">
-        <v>770.3</v>
+        <v>986.99</v>
       </c>
       <c r="H26" t="n">
-        <v>-313.53</v>
+        <v>-210.34</v>
       </c>
       <c r="I26" t="n">
-        <v>659.85</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-431.86</v>
+        <v>963.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
-        <v>3</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>virage_rapide</t>
-        </is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>26.13</v>
       </c>
       <c r="E27" t="n">
-        <v>72.15000000000001</v>
+        <v>32.32</v>
       </c>
       <c r="F27" t="n">
-        <v>-31.13</v>
+        <v>-210.34</v>
       </c>
       <c r="G27" t="n">
-        <v>659.85</v>
+        <v>963.88</v>
       </c>
       <c r="H27" t="n">
-        <v>-431.86</v>
+        <v>-233.71</v>
       </c>
       <c r="I27" t="n">
-        <v>599.03</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-468.99</v>
+        <v>952.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
-        <v>3</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ligne_droite</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>73.14</v>
       </c>
       <c r="E28" t="n">
-        <v>257.57</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-233.71</v>
       </c>
       <c r="G28" t="n">
-        <v>599.03</v>
+        <v>952.98</v>
       </c>
       <c r="H28" t="n">
-        <v>-468.99</v>
+        <v>-288.76</v>
       </c>
       <c r="I28" t="n">
-        <v>351.24</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-539.3</v>
+        <v>904.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
-        <v>3</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
           <t>chicane</t>
         </is>
       </c>
+      <c r="D29" t="n">
+        <v>32.53</v>
+      </c>
       <c r="E29" t="n">
-        <v>26.37</v>
+        <v>-43.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-38.27</v>
+        <v>-288.76</v>
       </c>
       <c r="G29" t="n">
-        <v>351.24</v>
+        <v>904.83</v>
       </c>
       <c r="H29" t="n">
-        <v>-539.3</v>
+        <v>-318.68</v>
       </c>
       <c r="I29" t="n">
-        <v>325.41</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-537.8200000000001</v>
+        <v>894.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
-        <v>3</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>liaison_chicane</t>
-        </is>
+      <c r="D30" t="n">
+        <v>163.14</v>
       </c>
       <c r="E30" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-318.68</v>
       </c>
       <c r="G30" t="n">
-        <v>325.41</v>
+        <v>894.16</v>
       </c>
       <c r="H30" t="n">
-        <v>-537.8200000000001</v>
+        <v>-481.73</v>
       </c>
       <c r="I30" t="n">
-        <v>253.06</v>
-      </c>
-      <c r="J30" t="n">
-        <v>-507.96</v>
+        <v>899.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
-        <v>3</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>chicane</t>
-        </is>
+          <t>virage_rapide</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>53.81</v>
       </c>
       <c r="E31" t="n">
-        <v>25.66</v>
+        <v>-30.27</v>
       </c>
       <c r="F31" t="n">
-        <v>32.16</v>
+        <v>-481.73</v>
       </c>
       <c r="G31" t="n">
-        <v>253.06</v>
+        <v>899.66</v>
       </c>
       <c r="H31" t="n">
-        <v>-507.96</v>
+        <v>-532.58</v>
       </c>
       <c r="I31" t="n">
-        <v>227.89</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-505.16</v>
+        <v>915.26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
-        <v>3</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ligne_droite</t>
-        </is>
+      <c r="D32" t="n">
+        <v>125.46</v>
       </c>
       <c r="E32" t="n">
-        <v>233.48</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-532.58</v>
       </c>
       <c r="G32" t="n">
-        <v>227.89</v>
+        <v>915.26</v>
       </c>
       <c r="H32" t="n">
-        <v>-505.16</v>
+        <v>-638.75</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-544.63</v>
+        <v>982.12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
-        <v>3</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>chicane</t>
-        </is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>62.01</v>
       </c>
       <c r="E33" t="n">
-        <v>29.22</v>
+        <v>152.01</v>
       </c>
       <c r="F33" t="n">
-        <v>-29.52</v>
+        <v>-638.75</v>
       </c>
       <c r="G33" t="n">
-        <v>-2.23</v>
+        <v>982.12</v>
       </c>
       <c r="H33" t="n">
-        <v>-544.63</v>
+        <v>-671.48</v>
       </c>
       <c r="I33" t="n">
-        <v>-31.01</v>
-      </c>
-      <c r="J33" t="n">
-        <v>-542.1</v>
+        <v>950.72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
-        <v>3</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>liaison_chicane</t>
-        </is>
+      <c r="D34" t="n">
+        <v>202.46</v>
       </c>
       <c r="E34" t="n">
-        <v>75.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-671.48</v>
       </c>
       <c r="G34" t="n">
-        <v>-31.01</v>
+        <v>950.72</v>
       </c>
       <c r="H34" t="n">
-        <v>-542.1</v>
+        <v>-570.8200000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-101.96</v>
-      </c>
-      <c r="J34" t="n">
-        <v>-516.58</v>
+        <v>775.0599999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
-        <v>3</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>virage</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>chicane</t>
-        </is>
+          <t>virage_rapide</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>90.29000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>32.83</v>
+        <v>43.6</v>
       </c>
       <c r="F35" t="n">
-        <v>41.83</v>
+        <v>-570.8200000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>-101.96</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>-516.58</v>
+        <v>-501.75</v>
       </c>
       <c r="I35" t="n">
-        <v>-134.06</v>
-      </c>
-      <c r="J35" t="n">
-        <v>-517.21</v>
+        <v>720.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
-        <v>3</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>ligne_droite</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="n">
+        <v>171.92</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-501.75</v>
+      </c>
+      <c r="G36" t="n">
+        <v>720.33</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-336.99</v>
+      </c>
+      <c r="I36" t="n">
+        <v>671.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-89.58</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-336.99</v>
+      </c>
+      <c r="G37" t="n">
+        <v>671.23</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-305.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>613.34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>226.57</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-305.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>613.34</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-368.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>395.74</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="E39" t="n">
+        <v>68.14</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-368.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>395.74</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-343.77</v>
+      </c>
+      <c r="I39" t="n">
+        <v>319.14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>130.57</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-343.77</v>
+      </c>
+      <c r="G40" t="n">
+        <v>319.14</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-240.92</v>
+      </c>
+      <c r="I40" t="n">
+        <v>238.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>virage_rapide</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>78.76000000000001</v>
+      </c>
+      <c r="E41" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-240.92</v>
+      </c>
+      <c r="G41" t="n">
+        <v>238.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-167.62</v>
+      </c>
+      <c r="I41" t="n">
+        <v>214.47</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>180.34</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-167.62</v>
+      </c>
+      <c r="G42" t="n">
+        <v>214.47</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="I42" t="n">
+        <v>219.03</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>76.34999999999999</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-158.35</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="G43" t="n">
+        <v>219.03</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>166.01</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>244.68</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>166.01</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-200.85</v>
+      </c>
+      <c r="I44" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>135.26</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-200.85</v>
+      </c>
+      <c r="G45" t="n">
+        <v>70</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-200.29</v>
+      </c>
+      <c r="I45" t="n">
+        <v>25.59</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>137.77</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-200.29</v>
+      </c>
+      <c r="G46" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-72.23</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-25.22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-81.84999999999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-72.23</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-25.22</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-28.21</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-110.02</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>166.11</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-28.21</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-110.02</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-66.95</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-271.55</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="E49" t="n">
+        <v>160.19</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-66.95</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-271.55</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-286.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-286.2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-206.97</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="E51" t="n">
+        <v>147.13</v>
+      </c>
+      <c r="F51" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-206.97</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-174.51</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>retour_stands</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>534.3</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-134.06</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-517.21</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="D52" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-174.51</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>0</v>
       </c>
     </row>

--- a/circuit.xlsx
+++ b/circuit.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>231.31</v>
+        <v>285.06</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>231.31</v>
+        <v>285.06</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -552,26 +552,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>virage_rapide</t>
+          <t>chicane</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>84.92</v>
+        <v>35.06</v>
       </c>
       <c r="E3" t="n">
-        <v>33.96</v>
+        <v>40.26</v>
       </c>
       <c r="F3" t="n">
-        <v>231.31</v>
+        <v>285.06</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>311.35</v>
+        <v>317.3</v>
       </c>
       <c r="I3" t="n">
-        <v>24.44</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="4">
@@ -585,26 +585,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ligne_droite</t>
+          <t>liaison_chicane</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>259.04</v>
+        <v>53.46</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>311.35</v>
+        <v>317.3</v>
       </c>
       <c r="G4" t="n">
-        <v>24.44</v>
+        <v>11.82</v>
       </c>
       <c r="H4" t="n">
-        <v>526.2</v>
+        <v>358.09</v>
       </c>
       <c r="I4" t="n">
-        <v>169.14</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="5">
@@ -618,26 +618,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>virage_rapide</t>
+          <t>chicane</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>98.18000000000001</v>
+        <v>16.57</v>
       </c>
       <c r="E5" t="n">
-        <v>-44.29</v>
+        <v>-31.5</v>
       </c>
       <c r="F5" t="n">
-        <v>526.2</v>
+        <v>358.09</v>
       </c>
       <c r="G5" t="n">
-        <v>169.14</v>
+        <v>46.37</v>
       </c>
       <c r="H5" t="n">
-        <v>619.92</v>
+        <v>372.97</v>
       </c>
       <c r="I5" t="n">
-        <v>188.74</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="6">
@@ -655,22 +655,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>171.18</v>
+        <v>159.79</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>619.92</v>
+        <v>372.97</v>
       </c>
       <c r="G6" t="n">
-        <v>188.74</v>
+        <v>53.16</v>
       </c>
       <c r="H6" t="n">
-        <v>788.3200000000001</v>
+        <v>530.9</v>
       </c>
       <c r="I6" t="n">
-        <v>158.03</v>
+        <v>77.51000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.26000000000001</v>
+        <v>92.91</v>
       </c>
       <c r="E7" t="n">
-        <v>84.76000000000001</v>
+        <v>93.81</v>
       </c>
       <c r="F7" t="n">
-        <v>788.3200000000001</v>
+        <v>530.9</v>
       </c>
       <c r="G7" t="n">
-        <v>158.03</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>863.45</v>
+        <v>577.63</v>
       </c>
       <c r="I7" t="n">
-        <v>205.06</v>
+        <v>145.95</v>
       </c>
     </row>
     <row r="8">
@@ -721,22 +721,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>141.48</v>
+        <v>204.78</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>863.45</v>
+        <v>577.63</v>
       </c>
       <c r="G8" t="n">
-        <v>205.06</v>
+        <v>145.95</v>
       </c>
       <c r="H8" t="n">
-        <v>901.4299999999999</v>
+        <v>533.04</v>
       </c>
       <c r="I8" t="n">
-        <v>341.35</v>
+        <v>345.82</v>
       </c>
     </row>
     <row r="9">
@@ -750,26 +750,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>virage_lent</t>
+          <t>chicane</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>84.66</v>
+        <v>31.18</v>
       </c>
       <c r="E9" t="n">
-        <v>79.37</v>
+        <v>32.53</v>
       </c>
       <c r="F9" t="n">
-        <v>901.4299999999999</v>
+        <v>533.04</v>
       </c>
       <c r="G9" t="n">
-        <v>341.35</v>
+        <v>345.82</v>
       </c>
       <c r="H9" t="n">
-        <v>869.55</v>
+        <v>518.1900000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>412.6</v>
+        <v>372.77</v>
       </c>
     </row>
     <row r="10">
@@ -783,26 +783,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ligne_droite</t>
+          <t>liaison_chicane</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>94.98999999999999</v>
+        <v>53.77</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>869.55</v>
+        <v>518.1900000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>412.6</v>
+        <v>372.77</v>
       </c>
       <c r="H10" t="n">
-        <v>784.3200000000001</v>
+        <v>480.1</v>
       </c>
       <c r="I10" t="n">
-        <v>454.54</v>
+        <v>410.72</v>
       </c>
     </row>
     <row r="11">
@@ -816,26 +816,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>virage_rapide</t>
+          <t>chicane</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>82.01000000000001</v>
+        <v>29.88</v>
       </c>
       <c r="E11" t="n">
-        <v>-36.93</v>
+        <v>-33.95</v>
       </c>
       <c r="F11" t="n">
-        <v>784.3200000000001</v>
+        <v>480.1</v>
       </c>
       <c r="G11" t="n">
-        <v>454.54</v>
+        <v>410.72</v>
       </c>
       <c r="H11" t="n">
-        <v>727</v>
+        <v>466.22</v>
       </c>
       <c r="I11" t="n">
-        <v>511.2</v>
+        <v>436.69</v>
       </c>
     </row>
     <row r="12">
@@ -853,22 +853,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>105.37</v>
+        <v>132.75</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>727</v>
+        <v>466.22</v>
       </c>
       <c r="G12" t="n">
-        <v>511.2</v>
+        <v>436.69</v>
       </c>
       <c r="H12" t="n">
-        <v>679.38</v>
+        <v>440.53</v>
       </c>
       <c r="I12" t="n">
-        <v>605.2</v>
+        <v>566.9299999999999</v>
       </c>
     </row>
     <row r="13">
@@ -886,22 +886,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62.19</v>
+        <v>85.2</v>
       </c>
       <c r="E13" t="n">
-        <v>39.58</v>
+        <v>-39.58</v>
       </c>
       <c r="F13" t="n">
-        <v>679.38</v>
+        <v>440.53</v>
       </c>
       <c r="G13" t="n">
-        <v>605.2</v>
+        <v>566.9299999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>635.05</v>
+        <v>453.06</v>
       </c>
       <c r="I13" t="n">
-        <v>647.04</v>
+        <v>649.5</v>
       </c>
     </row>
     <row r="14">
@@ -919,22 +919,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>127.79</v>
+        <v>153.46</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>635.05</v>
+        <v>453.06</v>
       </c>
       <c r="G14" t="n">
-        <v>647.04</v>
+        <v>649.5</v>
       </c>
       <c r="H14" t="n">
-        <v>517.9</v>
+        <v>526.1</v>
       </c>
       <c r="I14" t="n">
-        <v>698.1</v>
+        <v>784.47</v>
       </c>
     </row>
     <row r="15">
@@ -948,26 +948,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>epingle</t>
+          <t>virage_rapide</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>56.73</v>
+        <v>80.17</v>
       </c>
       <c r="E15" t="n">
-        <v>131.49</v>
+        <v>32.04</v>
       </c>
       <c r="F15" t="n">
-        <v>517.9</v>
+        <v>526.1</v>
       </c>
       <c r="G15" t="n">
-        <v>698.1</v>
+        <v>784.47</v>
       </c>
       <c r="H15" t="n">
-        <v>484.51</v>
+        <v>543.08</v>
       </c>
       <c r="I15" t="n">
-        <v>667.83</v>
+        <v>861.75</v>
       </c>
     </row>
     <row r="16">
@@ -985,22 +985,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>131.16</v>
+        <v>149.27</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>484.51</v>
+        <v>543.08</v>
       </c>
       <c r="G16" t="n">
-        <v>667.83</v>
+        <v>861.75</v>
       </c>
       <c r="H16" t="n">
-        <v>524.92</v>
+        <v>533.65</v>
       </c>
       <c r="I16" t="n">
-        <v>543.05</v>
+        <v>1010.72</v>
       </c>
     </row>
     <row r="17">
@@ -1014,26 +1014,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>virage_rapide</t>
+          <t>virage_lent</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79.15000000000001</v>
+        <v>100.63</v>
       </c>
       <c r="E17" t="n">
-        <v>-43.72</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>524.92</v>
+        <v>533.65</v>
       </c>
       <c r="G17" t="n">
-        <v>543.05</v>
+        <v>1010.72</v>
       </c>
       <c r="H17" t="n">
-        <v>519.64</v>
+        <v>464.88</v>
       </c>
       <c r="I17" t="n">
-        <v>465.98</v>
+        <v>1068.94</v>
       </c>
     </row>
     <row r="18">
@@ -1047,26 +1047,1148 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>123.09</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>464.88</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1068.94</v>
+      </c>
+      <c r="H18" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1056.33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="E19" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="F19" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1056.33</v>
+      </c>
+      <c r="H19" t="n">
+        <v>323.15</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1046.52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>323.15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1046.52</v>
+      </c>
+      <c r="H20" t="n">
+        <v>280.78</v>
+      </c>
+      <c r="I20" t="n">
+        <v>999.47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>36</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-38.39</v>
+      </c>
+      <c r="F21" t="n">
+        <v>280.78</v>
+      </c>
+      <c r="G21" t="n">
+        <v>999.47</v>
+      </c>
+      <c r="H21" t="n">
+        <v>249.82</v>
+      </c>
+      <c r="I21" t="n">
+        <v>982.45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>206.34</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>249.82</v>
+      </c>
+      <c r="G22" t="n">
+        <v>982.45</v>
+      </c>
+      <c r="H22" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="I22" t="n">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-40.17</v>
+      </c>
+      <c r="F23" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="G23" t="n">
+        <v>948</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="I23" t="n">
+        <v>954.29</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="G24" t="n">
+        <v>954.29</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-33.88</v>
+      </c>
+      <c r="I24" t="n">
+        <v>981.61</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="E25" t="n">
+        <v>39.41</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-33.88</v>
+      </c>
+      <c r="G25" t="n">
+        <v>981.61</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-61.91</v>
+      </c>
+      <c r="I25" t="n">
+        <v>986.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>150.22</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-61.91</v>
+      </c>
+      <c r="G26" t="n">
+        <v>986.99</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-210.34</v>
+      </c>
+      <c r="I26" t="n">
+        <v>963.88</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="E27" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-210.34</v>
+      </c>
+      <c r="G27" t="n">
+        <v>963.88</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-233.71</v>
+      </c>
+      <c r="I27" t="n">
+        <v>952.98</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>liaison_chicane</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>73.14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-233.71</v>
+      </c>
+      <c r="G28" t="n">
+        <v>952.98</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-288.76</v>
+      </c>
+      <c r="I28" t="n">
+        <v>904.83</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>chicane</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-288.76</v>
+      </c>
+      <c r="G29" t="n">
+        <v>904.83</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-318.68</v>
+      </c>
+      <c r="I29" t="n">
+        <v>894.16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>163.14</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-318.68</v>
+      </c>
+      <c r="G30" t="n">
+        <v>894.16</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-481.73</v>
+      </c>
+      <c r="I30" t="n">
+        <v>899.66</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>virage_rapide</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>53.81</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-30.27</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-481.73</v>
+      </c>
+      <c r="G31" t="n">
+        <v>899.66</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-532.58</v>
+      </c>
+      <c r="I31" t="n">
+        <v>915.26</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>125.46</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-532.58</v>
+      </c>
+      <c r="G32" t="n">
+        <v>915.26</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-638.75</v>
+      </c>
+      <c r="I32" t="n">
+        <v>982.12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>62.01</v>
+      </c>
+      <c r="E33" t="n">
+        <v>152.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-638.75</v>
+      </c>
+      <c r="G33" t="n">
+        <v>982.12</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-671.48</v>
+      </c>
+      <c r="I33" t="n">
+        <v>950.72</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>202.46</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-671.48</v>
+      </c>
+      <c r="G34" t="n">
+        <v>950.72</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-570.8200000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>775.0599999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>virage_rapide</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>90.29000000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-570.8200000000001</v>
+      </c>
+      <c r="G35" t="n">
+        <v>775.0599999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-501.75</v>
+      </c>
+      <c r="I35" t="n">
+        <v>720.33</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>171.92</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-501.75</v>
+      </c>
+      <c r="G36" t="n">
+        <v>720.33</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-336.99</v>
+      </c>
+      <c r="I36" t="n">
+        <v>671.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-89.58</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-336.99</v>
+      </c>
+      <c r="G37" t="n">
+        <v>671.23</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-305.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>613.34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>226.57</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-305.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>613.34</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-368.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>395.74</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="E39" t="n">
+        <v>68.14</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-368.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>395.74</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-343.77</v>
+      </c>
+      <c r="I39" t="n">
+        <v>319.14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>130.57</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-343.77</v>
+      </c>
+      <c r="G40" t="n">
+        <v>319.14</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-240.92</v>
+      </c>
+      <c r="I40" t="n">
+        <v>238.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>virage_rapide</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>78.76000000000001</v>
+      </c>
+      <c r="E41" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-240.92</v>
+      </c>
+      <c r="G41" t="n">
+        <v>238.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-167.62</v>
+      </c>
+      <c r="I41" t="n">
+        <v>214.47</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>180.34</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-167.62</v>
+      </c>
+      <c r="G42" t="n">
+        <v>214.47</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="I42" t="n">
+        <v>219.03</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>76.34999999999999</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-158.35</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="G43" t="n">
+        <v>219.03</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>166.01</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>244.68</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>166.01</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-200.85</v>
+      </c>
+      <c r="I44" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>135.26</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-200.85</v>
+      </c>
+      <c r="G45" t="n">
+        <v>70</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-200.29</v>
+      </c>
+      <c r="I45" t="n">
+        <v>25.59</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>137.77</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-200.29</v>
+      </c>
+      <c r="G46" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-72.23</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-25.22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>virage_lent</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-81.84999999999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-72.23</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-25.22</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-28.21</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-110.02</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>166.11</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-28.21</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-110.02</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-66.95</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-271.55</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="E49" t="n">
+        <v>160.19</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-66.95</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-271.55</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-286.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-286.2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-206.97</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>virage</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>epingle</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="E51" t="n">
+        <v>147.13</v>
+      </c>
+      <c r="F51" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-206.97</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-174.51</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ligne_droite</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>retour_stands</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>697.97</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>519.64</v>
-      </c>
-      <c r="G18" t="n">
-        <v>465.98</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0</v>
+      <c r="D52" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-174.51</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
